--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487110_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487110_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6367</v>
+        <v>4.6628</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8606</v>
+        <v>3.6994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7761</v>
+        <v>0.9635</v>
       </c>
       <c r="G2" t="n">
         <v>1.9161</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6425</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0417</v>
+        <v>-0.2029</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6009</v>
+        <v>-0.4135</v>
       </c>
       <c r="V2" t="n">
         <v>2.784</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3808</v>
+        <v>3.7139</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6623</v>
+        <v>1.7813</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7185</v>
+        <v>1.9326</v>
       </c>
       <c r="G3" t="n">
         <v>2.775</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1124</v>
+        <v>0.4455</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0912</v>
+        <v>0.0278</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2036</v>
+        <v>0.4177</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8576</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9152</v>
+        <v>2.1442</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9166</v>
+        <v>-0.0789</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8318</v>
+        <v>2.223</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0582</v>
+        <v>1.857</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7926</v>
+        <v>0.2598</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2656</v>
+        <v>1.5973</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3059</v>
+        <v>2.0571</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1996</v>
+        <v>0.714</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1064</v>
+        <v>1.3431</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2477</v>
+        <v>-0.2001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4069</v>
+        <v>-0.4542</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1592</v>
+        <v>0.2542</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8951</v>
+        <v>0.193</v>
       </c>
       <c r="Q4" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.1231</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.2059</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.0281</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.8951</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1785</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.1824</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.3608</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.8999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.5717</v>
       </c>
       <c r="X4" t="n">
         <v>0.3281</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6504</v>
+        <v>1.5959</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4388</v>
+        <v>-1.7004</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0892</v>
+        <v>3.2964</v>
       </c>
       <c r="G5" t="n">
-        <v>1.857</v>
+        <v>-2.0582</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2598</v>
+        <v>-1.7926</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5973</v>
+        <v>-0.2656</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0571</v>
+        <v>-2.3059</v>
       </c>
       <c r="K5" t="n">
-        <v>0.714</v>
+        <v>-2.1996</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3431</v>
+        <v>-0.1064</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2001</v>
+        <v>0.2477</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4542</v>
+        <v>0.4069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2542</v>
+        <v>-0.1592</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>2.8951</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1231</v>
+        <v>2.8951</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7277</v>
+        <v>-0.1408</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5658</v>
+        <v>0.0338</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.162</v>
+        <v>-0.1745</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3281</v>
+        <v>0.8999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X5" t="n">
         <v>0.3281</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0935</v>
+        <v>0.7385</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6034</v>
+        <v>-0.7442</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6969</v>
+        <v>1.4828</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2835</v>
@@ -922,13 +922,13 @@
         <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3926</v>
+        <v>0.0377</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0132</v>
+        <v>-0.1276</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3794</v>
+        <v>0.1652</v>
       </c>
       <c r="V6" t="n">
         <v>0.9843</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. NUÑEZ HERRERO</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5316</v>
+        <v>0.2253</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1776</v>
+        <v>0.2169</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7092</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.149</v>
+        <v>-0.5132</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3364</v>
+        <v>-0.0134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8125</v>
+        <v>-0.4998</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2288</v>
+        <v>-0.2129</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0157</v>
+        <v>0.414</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2131</v>
+        <v>-0.6269</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0798</v>
+        <v>-0.3003</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3207</v>
+        <v>-0.4274</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4006</v>
+        <v>0.1271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7021</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6227</v>
+        <v>-0.1035</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6954</v>
+        <v>-0.119</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0727</v>
+        <v>0.0155</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>R. NUÑEZ HERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0914</v>
+        <v>0.0091</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2169</v>
+        <v>-2.7001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1255</v>
+        <v>2.7092</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5132</v>
+        <v>-1.149</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0134</v>
+        <v>-0.3364</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4998</v>
+        <v>-0.8125</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2129</v>
+        <v>-1.2288</v>
       </c>
       <c r="K8" t="n">
-        <v>0.414</v>
+        <v>-0.0157</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6269</v>
+        <v>-1.2131</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3003</v>
+        <v>0.0798</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4274</v>
+        <v>-0.3207</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1271</v>
+        <v>0.4006</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.579</v>
+        <v>2.7021</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2373</v>
+        <v>0.1001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.119</v>
+        <v>0.1729</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1183</v>
+        <v>-0.0727</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2878</v>
+        <v>-0.3171</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9565</v>
+        <v>-0.0394</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3313</v>
+        <v>-0.2778</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0276</v>
@@ -1156,13 +1156,13 @@
         <v>3.0881</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3458</v>
+        <v>-0.3751</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.969</v>
+        <v>-0.0518</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3768</v>
+        <v>-0.3233</v>
       </c>
       <c r="V9" t="n">
         <v>0.8576</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3648</v>
+        <v>-1.7822</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5558</v>
+        <v>-3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.191</v>
+        <v>1.2177</v>
       </c>
       <c r="G10" t="n">
         <v>-2.121</v>
@@ -1234,13 +1234,13 @@
         <v>3.0881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8031</v>
+        <v>0.3857</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0946</v>
+        <v>0.6504</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2915</v>
+        <v>-0.2648</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1701</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0831</v>
+        <v>-4.3445</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.503</v>
+        <v>-3.7644</v>
       </c>
       <c r="F11" t="n">
         <v>-0.5800999999999999</v>
@@ -1312,10 +1312,10 @@
         <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.203</v>
+        <v>-0.4643</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8632</v>
+        <v>-0.1246</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3398</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.563899999999999</v>
+        <v>6.645899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.411899999999999</v>
+        <v>-6.329800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>12.9758</v>
+        <v>12.9757</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9707</v>
@@ -1378,7 +1378,7 @@
         <v>-2.2394</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1604999999999999</v>
+        <v>-0.1605000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>6.7553</v>
@@ -1390,13 +1390,13 @@
         <v>22.1958</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.047</v>
+        <v>-0.9650999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.0291</v>
+        <v>0.05309999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0182</v>
+        <v>-1.0183</v>
       </c>
       <c r="V12" t="n">
         <v>2.8263</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4202</v>
+        <v>3.0444</v>
       </c>
       <c r="E13" t="n">
-        <v>1.182</v>
+        <v>-0.2199</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2382</v>
+        <v>3.2643</v>
       </c>
       <c r="G13" t="n">
         <v>2.2384</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>2.675</v>
+        <v>1.2992</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0451</v>
+        <v>0.6432</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6299</v>
+        <v>0.656</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4932</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0324</v>
+        <v>2.1136</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5736</v>
+        <v>-0.715</v>
       </c>
       <c r="F14" t="n">
-        <v>2.606</v>
+        <v>2.8286</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0227</v>
+        <v>3.7413</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.179</v>
+        <v>2.6217</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2017</v>
+        <v>1.1196</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3621</v>
+        <v>3.3998</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3621</v>
+        <v>2.3752</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.0247</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6605</v>
+        <v>0.3415</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5411</v>
+        <v>0.2466</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2017</v>
+        <v>0.0949</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.158</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8951</v>
+        <v>-5.7902</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.2201</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1018</v>
+        <v>-0.4524</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4098</v>
+        <v>0.6725</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6562</v>
+        <v>1.4333</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8576</v>
+        <v>2.1278</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2014</v>
+        <v>-0.6945</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8921</v>
+        <v>1.256</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6163</v>
+        <v>0.9149</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5083</v>
+        <v>0.3411</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7413</v>
+        <v>-1.3673</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6217</v>
+        <v>-0.8953</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1196</v>
+        <v>-0.472</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3998</v>
+        <v>0.1744</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3752</v>
+        <v>0.093</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0247</v>
+        <v>0.0814</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3415</v>
+        <v>-1.5417</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2466</v>
+        <v>-0.9883</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0949</v>
+        <v>-0.5534</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.2811</v>
+        <v>0.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0014</v>
+        <v>0.8163</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3537</v>
+        <v>0.1917</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3522</v>
+        <v>0.6246</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4333</v>
+        <v>1.228</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1278</v>
+        <v>1.5138</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6945</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8826000000000001</v>
+        <v>1.2522</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5144</v>
+        <v>-1.2731</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3682</v>
+        <v>2.5254</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3673</v>
+        <v>1.0227</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8953</v>
+        <v>-0.179</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.472</v>
+        <v>1.2017</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1744</v>
+        <v>0.3621</v>
       </c>
       <c r="K16" t="n">
-        <v>0.093</v>
+        <v>0.3621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5417</v>
+        <v>0.6605</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9883</v>
+        <v>-0.5411</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5534</v>
+        <v>1.2017</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4429</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2089</v>
+        <v>0.4022</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.3291</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>0.6562</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5138</v>
+        <v>0.8576</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>-0.2014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2218</v>
+        <v>0.1702</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1022</v>
+        <v>-1.2657</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1196</v>
+        <v>1.4359</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5436</v>
+        <v>-0.6977</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2276</v>
+        <v>0.1099</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6840000000000001</v>
+        <v>-0.8076</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3434</v>
+        <v>-0.8177</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0404</v>
+        <v>0.5175</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3838</v>
+        <v>-1.3352</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.887</v>
+        <v>0.12</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1872</v>
+        <v>-0.4076</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6998</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5064</v>
+        <v>0.3417</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8971</v>
+        <v>-0.0317</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3907</v>
+        <v>0.3734</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4126</v>
+        <v>1.1052</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4126</v>
+        <v>1.5138</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4167</v>
+        <v>-0.1408</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3933</v>
+        <v>0.2517</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.3925</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9003</v>
+        <v>-1.7991</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5422</v>
+        <v>-0.1904</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3581</v>
+        <v>-1.6087</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1185</v>
+        <v>-1.2317</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4023</v>
+        <v>0.1035</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7161999999999999</v>
+        <v>-1.3352</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7818000000000001</v>
+        <v>-0.5674</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1399</v>
+        <v>-0.2939</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6419</v>
+        <v>-0.2735</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.579</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0383</v>
+        <v>0.1372</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2049</v>
+        <v>0.2555</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2433</v>
+        <v>-0.1183</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.6996</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.6996</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4947</v>
+        <v>-0.1703</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0487</v>
+        <v>-1.3524</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4461</v>
+        <v>1.1821</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7991</v>
+        <v>-0.3197</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1904</v>
+        <v>0.2516</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6087</v>
+        <v>-0.5712</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2317</v>
+        <v>-0.4006</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1035</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3352</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5674</v>
+        <v>0.081</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2939</v>
+        <v>0.7743</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2735</v>
+        <v>-0.6933</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.7371</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7281</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.7148</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-1.3508</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.2168</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.0449</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.1719</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.9421</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.228</v>
-      </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.677</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.753</v>
+        <v>-0.1074</v>
       </c>
       <c r="F20" t="n">
-        <v>1.076</v>
+        <v>-0.623</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3197</v>
+        <v>2.9003</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2516</v>
+        <v>1.5422</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5712</v>
+        <v>1.3581</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4006</v>
+        <v>2.1185</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5227000000000001</v>
+        <v>1.4023</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1221</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.081</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7743</v>
+        <v>0.1399</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6933</v>
+        <v>0.6419</v>
       </c>
       <c r="P20" t="n">
-        <v>0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2214</v>
+        <v>-0.352</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3873</v>
+        <v>-0.2958</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6087</v>
+        <v>-0.0562</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3508</v>
+        <v>-2.6996</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3508</v>
+        <v>-2.6996</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0322</v>
+        <v>-1.1423</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0668</v>
+        <v>-1.5042</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0346</v>
+        <v>0.362</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6977</v>
+        <v>-0.5436</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1099</v>
+        <v>-1.2276</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8076</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8177</v>
+        <v>0.3434</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5175</v>
+        <v>-1.0404</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3352</v>
+        <v>1.3838</v>
       </c>
       <c r="M21" t="n">
-        <v>0.12</v>
+        <v>-0.887</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4076</v>
+        <v>-0.1872</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8606</v>
+        <v>0.586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8328</v>
+        <v>0.4951</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0278</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1052</v>
+        <v>-0.4126</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5138</v>
+        <v>-0.4126</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9492</v>
+        <v>-3.2274</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6322</v>
+        <v>-3.2316</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.317</v>
+        <v>0.0042</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3464</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4098</v>
+        <v>0.312</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5354</v>
+        <v>-0.1348</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1256</v>
+        <v>0.4468</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9996</v>
+        <v>-4.9863</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2727</v>
+        <v>-4.473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7269</v>
+        <v>-0.5134</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8583</v>
@@ -2248,13 +2248,13 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2168</v>
+        <v>0.23</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1322</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.2981</v>
       </c>
       <c r="V23" t="n">
         <v>-2.007</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5639</v>
+        <v>-2.561</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.9758</v>
+        <v>-12.9757</v>
       </c>
       <c r="F24" t="n">
-        <v>8.4117</v>
+        <v>10.4147</v>
       </c>
       <c r="G24" t="n">
-        <v>1.970599999999999</v>
+        <v>1.9706</v>
       </c>
       <c r="H24" t="n">
         <v>1.335300000000001</v>
@@ -2302,7 +2302,7 @@
         <v>2.4002</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2394</v>
+        <v>2.239399999999999</v>
       </c>
       <c r="L24" t="n">
         <v>0.1608999999999997</v>
@@ -2314,7 +2314,7 @@
         <v>-0.9039999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4746999999999997</v>
+        <v>0.4747</v>
       </c>
       <c r="P24" t="n">
         <v>-6.755199999999999</v>
@@ -2326,19 +2326,19 @@
         <v>15.4407</v>
       </c>
       <c r="S24" t="n">
-        <v>3.0472</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>1.0181</v>
       </c>
       <c r="U24" t="n">
-        <v>2.0288</v>
+        <v>4.0317</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8264</v>
       </c>
       <c r="W24" t="n">
-        <v>5.8018</v>
+        <v>5.801799999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-8.628399999999999</v>
